--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120.08542</v>
+        <v>16.87987</v>
       </c>
       <c r="D2" t="n">
-        <v>86.28395999999999</v>
+        <v>16.34706</v>
       </c>
       <c r="E2" t="n">
-        <v>91.21827999999999</v>
+        <v>16.63753</v>
       </c>
       <c r="F2" t="n">
-        <v>520.20376</v>
+        <v>42.10935</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.81141</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.17914</v>
+        <v>16.88629</v>
       </c>
       <c r="D3" t="n">
-        <v>85.44999</v>
+        <v>16.68149</v>
       </c>
       <c r="E3" t="n">
-        <v>92.11997</v>
+        <v>16.70056</v>
       </c>
       <c r="F3" t="n">
-        <v>517.135</v>
+        <v>42.59152</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.81595</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122.11856</v>
+        <v>17.14952</v>
       </c>
       <c r="D4" t="n">
-        <v>86.35986</v>
+        <v>16.70287</v>
       </c>
       <c r="E4" t="n">
-        <v>90.78088</v>
+        <v>16.97643</v>
       </c>
       <c r="F4" t="n">
-        <v>534.44882</v>
+        <v>42.66902</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.81637</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120.72418</v>
+        <v>16.97514</v>
       </c>
       <c r="D5" t="n">
-        <v>84.97563</v>
+        <v>16.33286</v>
       </c>
       <c r="E5" t="n">
-        <v>90.17838999999999</v>
+        <v>16.74683</v>
       </c>
       <c r="F5" t="n">
-        <v>510.69123</v>
+        <v>42.76158</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.7828</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.26767</v>
+        <v>16.8449</v>
       </c>
       <c r="D6" t="n">
-        <v>84.89516</v>
+        <v>16.47513</v>
       </c>
       <c r="E6" t="n">
-        <v>91.58993</v>
+        <v>16.67282</v>
       </c>
       <c r="F6" t="n">
-        <v>509.74332</v>
+        <v>42.11551</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04968</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83833</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>121.1091</v>
+        <v>17.16836</v>
       </c>
       <c r="D7" t="n">
-        <v>85.67131000000001</v>
+        <v>16.55041</v>
       </c>
       <c r="E7" t="n">
-        <v>91.48757999999999</v>
+        <v>16.8655</v>
       </c>
       <c r="F7" t="n">
-        <v>508.59134</v>
+        <v>42.75515</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.83075</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>121.97039</v>
+        <v>16.89402</v>
       </c>
       <c r="D8" t="n">
-        <v>85.90491</v>
+        <v>16.62552</v>
       </c>
       <c r="E8" t="n">
-        <v>92.40402</v>
+        <v>16.68184</v>
       </c>
       <c r="F8" t="n">
-        <v>515.78838</v>
+        <v>42.68593</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.85715</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120.23029</v>
+        <v>16.84824</v>
       </c>
       <c r="D9" t="n">
-        <v>86.14011000000001</v>
+        <v>16.53241</v>
       </c>
       <c r="E9" t="n">
-        <v>90.08853000000001</v>
+        <v>16.80404</v>
       </c>
       <c r="F9" t="n">
-        <v>508.09468</v>
+        <v>42.55913</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.81507</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123.39612</v>
+        <v>16.5995</v>
       </c>
       <c r="D10" t="n">
-        <v>86.83861</v>
+        <v>16.29496</v>
       </c>
       <c r="E10" t="n">
-        <v>90.09275</v>
+        <v>16.48396</v>
       </c>
       <c r="F10" t="n">
-        <v>523.08024</v>
+        <v>42.85691</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.85815</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.71565</v>
+        <v>17.04461</v>
       </c>
       <c r="D12" t="n">
-        <v>24.35166</v>
+        <v>16.37947</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.54858</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.29922</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.80016</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.58822</v>
+        <v>17.00202</v>
       </c>
       <c r="D13" t="n">
-        <v>24.42975</v>
+        <v>16.33127</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.6445</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.22084</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.80109</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.511089999999999</v>
+        <v>16.9084</v>
       </c>
       <c r="D14" t="n">
-        <v>24.44299</v>
+        <v>16.325</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.7872</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.47311</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.77156</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.69181</v>
+        <v>16.80137</v>
       </c>
       <c r="D15" t="n">
-        <v>24.6292</v>
+        <v>16.61689</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.68554</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.09641</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.88028</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.56165</v>
+        <v>16.7083</v>
       </c>
       <c r="D16" t="n">
-        <v>24.14074</v>
+        <v>16.30962</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.64463</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.09358</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84878</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.59469</v>
+        <v>16.85596</v>
       </c>
       <c r="D17" t="n">
-        <v>24.41625</v>
+        <v>16.57131</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.76978</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.4371</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84749</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.56916</v>
+        <v>17.0812</v>
       </c>
       <c r="D18" t="n">
-        <v>23.74549</v>
+        <v>16.83632</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.85785</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.15707</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.77759</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.5212</v>
+        <v>16.79254</v>
       </c>
       <c r="D19" t="n">
-        <v>24.21797</v>
+        <v>16.48243</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.60388</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.14246</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83419</v>
       </c>
     </row>
     <row r="20">
@@ -742,10 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.64803</v>
+        <v>16.72163</v>
       </c>
       <c r="D20" t="n">
-        <v>24.5196</v>
+        <v>16.14143</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.62604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.69307</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81883</v>
       </c>
     </row>
     <row r="21">
@@ -769,16 +961,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -788,26 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.66677</v>
+        <v>15.89728</v>
       </c>
       <c r="D22" t="n">
-        <v>16.67678</v>
+        <v>15.75033</v>
       </c>
       <c r="E22" t="n">
-        <v>16.70788</v>
+        <v>15.86175</v>
       </c>
       <c r="F22" t="n">
-        <v>43.25807</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05133</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.79293</v>
+        <v>250.70788</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.81327</v>
+        <v>15.75617</v>
       </c>
       <c r="D23" t="n">
-        <v>16.66931</v>
+        <v>15.36633</v>
       </c>
       <c r="E23" t="n">
-        <v>16.35332</v>
+        <v>15.53181</v>
       </c>
       <c r="F23" t="n">
-        <v>42.73439</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.82262</v>
+        <v>253.67595</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.87915</v>
+        <v>15.71672</v>
       </c>
       <c r="D24" t="n">
-        <v>16.60314</v>
+        <v>15.53683</v>
       </c>
       <c r="E24" t="n">
-        <v>16.61051</v>
+        <v>15.5547</v>
       </c>
       <c r="F24" t="n">
-        <v>42.89725</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05118</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.78943</v>
+        <v>253.26104</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.77185</v>
+        <v>15.85684</v>
       </c>
       <c r="D25" t="n">
-        <v>16.66437</v>
+        <v>15.56297</v>
       </c>
       <c r="E25" t="n">
-        <v>16.66589</v>
+        <v>15.62905</v>
       </c>
       <c r="F25" t="n">
-        <v>41.74328</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.05081</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.81583</v>
+        <v>253.84554</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.72362</v>
+        <v>15.72253</v>
       </c>
       <c r="D26" t="n">
-        <v>16.49822</v>
+        <v>15.57008</v>
       </c>
       <c r="E26" t="n">
-        <v>16.64426</v>
+        <v>15.69924</v>
       </c>
       <c r="F26" t="n">
-        <v>42.50529</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05041</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.78857</v>
+        <v>249.67069</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.19651</v>
+        <v>15.93318</v>
       </c>
       <c r="D27" t="n">
-        <v>16.47403</v>
+        <v>15.41905</v>
       </c>
       <c r="E27" t="n">
-        <v>16.80349</v>
+        <v>15.70937</v>
       </c>
       <c r="F27" t="n">
-        <v>42.31205</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05037</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.82272</v>
+        <v>251.08531</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.45497</v>
+        <v>15.84139</v>
       </c>
       <c r="D28" t="n">
-        <v>16.50163</v>
+        <v>15.61917</v>
       </c>
       <c r="E28" t="n">
-        <v>16.81419</v>
+        <v>15.80385</v>
       </c>
       <c r="F28" t="n">
-        <v>42.43577</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05022</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.80875</v>
+        <v>256.0587</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.79918</v>
+        <v>15.67291</v>
       </c>
       <c r="D29" t="n">
-        <v>16.28829</v>
+        <v>15.26592</v>
       </c>
       <c r="E29" t="n">
-        <v>16.49076</v>
+        <v>15.60706</v>
       </c>
       <c r="F29" t="n">
-        <v>42.40722</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.04984</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.81976</v>
+        <v>255.6743</v>
       </c>
     </row>
     <row r="30">
@@ -992,63 +1126,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.57388</v>
+        <v>15.87768</v>
       </c>
       <c r="D30" t="n">
-        <v>16.47272</v>
+        <v>15.32331</v>
       </c>
       <c r="E30" t="n">
-        <v>16.60777</v>
+        <v>15.65702</v>
       </c>
       <c r="F30" t="n">
-        <v>42.81673</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05114</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.81656</v>
+        <v>253.40886</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.75178</v>
+        <v>16.58929</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08169</v>
+        <v>16.03833</v>
       </c>
       <c r="E32" t="n">
-        <v>0.60268</v>
+        <v>16.16077</v>
       </c>
       <c r="F32" t="n">
-        <v>0.97893</v>
+        <v>21.5463</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11025</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09242</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12424</v>
+        <v>34.17985</v>
       </c>
     </row>
     <row r="33">
@@ -1095,28 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.75421</v>
+        <v>16.68728</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08086</v>
+        <v>16.12967</v>
       </c>
       <c r="E33" t="n">
-        <v>0.60822</v>
+        <v>16.4113</v>
       </c>
       <c r="F33" t="n">
-        <v>0.95346</v>
+        <v>21.94294</v>
       </c>
       <c r="G33" t="n">
-        <v>0.10895</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09378</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12616</v>
+        <v>35.09243</v>
       </c>
     </row>
     <row r="34">
@@ -1126,28 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.74707</v>
+        <v>16.82441</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08112</v>
+        <v>15.78882</v>
       </c>
       <c r="E34" t="n">
-        <v>0.62066</v>
+        <v>16.10779</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96016</v>
+        <v>22.11484</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11024</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09268999999999999</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12668</v>
+        <v>34.88249</v>
       </c>
     </row>
     <row r="35">
@@ -1157,28 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7454499999999999</v>
+        <v>16.68408</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08029</v>
+        <v>16.10314</v>
       </c>
       <c r="E35" t="n">
-        <v>0.61602</v>
+        <v>16.39533</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95494</v>
+        <v>21.88927</v>
       </c>
       <c r="G35" t="n">
-        <v>0.10953</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09424</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.12557</v>
+        <v>34.71357</v>
       </c>
     </row>
     <row r="36">
@@ -1188,28 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7471100000000001</v>
+        <v>16.77061</v>
       </c>
       <c r="D36" t="n">
-        <v>0.07976999999999999</v>
+        <v>16.10876</v>
       </c>
       <c r="E36" t="n">
-        <v>0.59828</v>
+        <v>16.2059</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9579800000000001</v>
+        <v>21.2772</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10938</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09358</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12474</v>
+        <v>34.87574</v>
       </c>
     </row>
     <row r="37">
@@ -1219,28 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.757</v>
+        <v>16.72243</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07976999999999999</v>
+        <v>16.00394</v>
       </c>
       <c r="E37" t="n">
-        <v>0.59245</v>
+        <v>16.28072</v>
       </c>
       <c r="F37" t="n">
-        <v>0.98826</v>
+        <v>21.44254</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10988</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09202</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12389</v>
+        <v>33.74561</v>
       </c>
     </row>
     <row r="38">
@@ -1250,28 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.75405</v>
+        <v>16.86727</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08081000000000001</v>
+        <v>15.82103</v>
       </c>
       <c r="E38" t="n">
-        <v>0.61765</v>
+        <v>16.34954</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96712</v>
+        <v>21.82987</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1087</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09227</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.12373</v>
+        <v>34.50091</v>
       </c>
     </row>
     <row r="39">
@@ -1281,28 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.74015</v>
+        <v>16.52305</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08187999999999999</v>
+        <v>15.95753</v>
       </c>
       <c r="E39" t="n">
-        <v>0.60318</v>
+        <v>16.3248</v>
       </c>
       <c r="F39" t="n">
-        <v>0.96736</v>
+        <v>22.13031</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10812</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09378</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.12761</v>
+        <v>34.31946</v>
       </c>
     </row>
     <row r="40">
@@ -1312,28 +1353,843 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.75392</v>
+        <v>16.91355</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07965</v>
+        <v>16.15853</v>
       </c>
       <c r="E40" t="n">
-        <v>0.62098</v>
+        <v>16.24576</v>
       </c>
       <c r="F40" t="n">
-        <v>0.97011</v>
+        <v>21.37705</v>
       </c>
       <c r="G40" t="n">
-        <v>0.10818</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09241000000000001</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12445</v>
+        <v>33.93467</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.78935</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.27197</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.36855</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.80353</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.15846</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.66831</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.04198</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.49406</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.69697</v>
+      </c>
+      <c r="G43" t="n">
+        <v>32.80046</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.55818</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.6122</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.46982</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.60689</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.48691</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.81942</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.01521</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.0507</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.64691</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.40782</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.82513</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.99096</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.26301</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.64176</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.20623</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.54933</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.92356</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.23848</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.96336</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.10533</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.6574</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.85135</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.62454</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.88705</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.7335</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.08214</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.54701</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.08353</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.71423</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.04805</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.70886</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.0337</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.39895</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.61137</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.68046</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61213</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.1189</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60158</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.14635</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61075</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.10875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.11702</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60465</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11222</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60726</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.11161</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.10867</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.59784</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.11554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.62712</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.1078</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.5924</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11538</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.59824</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11207</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61374</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11067</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.6067</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.13789</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6095</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.10668</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61346</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.08521</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.60862</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.13026</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.61589</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.10518</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60906</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.08272</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.75212</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.07978</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.9592000000000001</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10988</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09343</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12412</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.73702</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.60985</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95556</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10996</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12764</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.76871</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.07990999999999999</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60629</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.97668</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10887</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12514</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.74327</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.59667</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.97171</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10759</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09243</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12692</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.73886</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08065</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.59894</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.96757</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10902</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09382</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12802</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.74818</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08255999999999999</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9445</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11029</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09225</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12796</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.74853</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08075</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60749</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10796</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09251</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12709</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75241</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60141</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.96595</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09197</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.1274</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.74555</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08129</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.10916</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.126</v>
       </c>
     </row>
   </sheetData>
